--- a/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed1train/score_seed1train.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed1train/score_seed1train.xlsx
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.99984039080938</v>
+        <v>0.9998403908093799</v>
       </c>
       <c r="E166" t="n">
         <v>0.995239714382863</v>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.9924225338499085</v>
+        <v>0.9924225338499086</v>
       </c>
       <c r="E177" t="n">
         <v>0.969786293294031</v>
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.9996286246828739</v>
+        <v>0.9996286246828737</v>
       </c>
       <c r="E190" t="n">
         <v>0.9943896633798028</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.9994481668588813</v>
+        <v>0.9994481668588812</v>
       </c>
       <c r="E236" t="n">
         <v>0.9916978674914537</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.9995135515626611</v>
+        <v>0.999513551562661</v>
       </c>
       <c r="E241" t="n">
         <v>0.9964297857871472</v>
